--- a/data/trans_bre/IP16_n_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Provincia-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 36,62</t>
+          <t>-28,06; 38,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 47,08</t>
+          <t>-1,69; 46,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,17; -4,0</t>
+          <t>-34,83; -3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 10,85</t>
+          <t>-20,04; 9,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 197,81</t>
+          <t>-49,98; 173,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,74; inf</t>
+          <t>-41,27; 1041,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 471,97</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 22,81</t>
+          <t>-28,68; 21,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 19,65</t>
+          <t>-5,88; 20,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,13; -2,75</t>
+          <t>-42,4; -3,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 11,98</t>
+          <t>-35,05; 13,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 73,46</t>
+          <t>-53,9; 76,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 735,41</t>
+          <t>-72,45; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-93,01; -0,45</t>
+          <t>-91,34; -0,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 38,15</t>
+          <t>-79,79; 43,07</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 49,19</t>
+          <t>-11,83; 52,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 26,07</t>
+          <t>-19,81; 26,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,41</t>
+          <t>0,0; 44,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 26,24</t>
+          <t>-20,69; 26,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 564,02</t>
+          <t>-41,49; 669,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 226,82</t>
+          <t>-70,58; 226,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,89; 230,43</t>
+          <t>-60,77; 226,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 2,98</t>
+          <t>-52,09; 4,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 17,21</t>
+          <t>-25,51; 17,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 30,66</t>
+          <t>0,42; 31,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 24,12</t>
+          <t>-49,25; 27,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 4,47</t>
+          <t>-72,92; 11,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-90,1; 518,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 1040,56</t>
+          <t>-17,12; 1350,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,53; 116,14</t>
+          <t>-77,83; 153,87</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 49,94</t>
+          <t>-28,75; 49,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 33,55</t>
+          <t>-16,88; 34,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 40,13</t>
+          <t>-26,16; 34,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 53,01</t>
+          <t>-11,64; 55,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,55; —</t>
+          <t>-60,58; 542,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-84,82; 717,84</t>
+          <t>-81,44; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 479,34</t>
+          <t>-28,22; 544,61</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 20,89</t>
+          <t>-45,16; 15,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 42,0</t>
+          <t>-1,11; 46,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 0,0</t>
+          <t>-60,69; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,36; -11,29</t>
+          <t>-61,24; -8,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,71; 39,79</t>
+          <t>-62,11; 32,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,02</t>
+          <t>-100,0; -10,04</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 8,44</t>
+          <t>-34,79; 9,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 23,98</t>
+          <t>-5,69; 24,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 37,81</t>
+          <t>-12,55; 36,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 34,66</t>
+          <t>-5,88; 37,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 35,13</t>
+          <t>-72,18; 35,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,15; —</t>
+          <t>-63,24; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-70,82; —</t>
+          <t>-69,03; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 138,75</t>
+          <t>-13,83; 153,23</t>
         </is>
       </c>
     </row>
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 27,72</t>
+          <t>-10,57; 26,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 1,13</t>
+          <t>-36,0; 3,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 13,12</t>
+          <t>-13,29; 11,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 26,55</t>
+          <t>-43,54; 25,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 143,56</t>
+          <t>-30,51; 132,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,4</t>
+          <t>-92,3; 71,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,64; 62,83</t>
+          <t>-60,9; 54,8</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 8,17</t>
+          <t>-10,81; 8,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 11,17</t>
+          <t>-2,75; 11,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 5,62</t>
+          <t>-8,71; 5,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 5,33</t>
+          <t>-18,82; 4,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 22,62</t>
+          <t>-24,67; 23,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 102,95</t>
+          <t>-17,52; 110,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 57,72</t>
+          <t>-50,38; 45,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 17,77</t>
+          <t>-48,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-23,4%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 38,41</t>
+          <t>-30,14; 35,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 46,65</t>
+          <t>-2,47; 48,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,83; -3,98</t>
+          <t>-30,62; -3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 9,56</t>
+          <t>-16,73; 15,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 173,19</t>
+          <t>-52,57; 178,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 1041,56</t>
+          <t>-25,67; 1106,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 722,57</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-10,78</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-31,79%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 21,86</t>
+          <t>-26,84; 22,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 20,73</t>
+          <t>-6,63; 21,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,4; -3,47</t>
+          <t>-41,52; -3,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 13,26</t>
+          <t>-16,11; 20,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 76,27</t>
+          <t>-49,76; 74,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,45; —</t>
+          <t>-72,62; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,34; -0,48</t>
+          <t>-92,29; -2,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,79; 43,07</t>
+          <t>-40,19; 77,27</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 52,08</t>
+          <t>-13,81; 47,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 26,77</t>
+          <t>-19,53; 26,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,19</t>
+          <t>0,0; 44,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 26,41</t>
+          <t>-17,17; 28,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 669,04</t>
+          <t>-39,86; 629,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 226,61</t>
+          <t>-68,8; 229,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 226,46</t>
+          <t>-54,61; 297,91</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-12,42</t>
+          <t>-10,94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,41%</t>
+          <t>-24,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 4,84</t>
+          <t>-50,93; 3,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 17,42</t>
+          <t>-25,94; 16,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 31,89</t>
+          <t>-0,41; 34,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,25; 27,47</t>
+          <t>-43,68; 28,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,92; 11,45</t>
+          <t>-72,61; 7,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,1; 518,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 1350,71</t>
+          <t>-18,71; 1292,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 153,87</t>
+          <t>-72,61; 174,45</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,68</t>
+          <t>22,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 49,1</t>
+          <t>-29,22; 50,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 34,24</t>
+          <t>-20,62; 33,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 34,76</t>
+          <t>-31,13; 38,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 55,81</t>
+          <t>-15,22; 53,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 542,96</t>
+          <t>-63,11; 499,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-81,44; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 544,61</t>
+          <t>-30,21; 413,38</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-37,55</t>
+          <t>-36,19</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-83,54%</t>
+          <t>-82,91%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 15,39</t>
+          <t>-43,92; 20,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 46,45</t>
+          <t>-3,72; 42,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 0,0</t>
+          <t>-59,14; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -8,68</t>
+          <t>-58,88; -10,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 32,16</t>
+          <t>-59,59; 43,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -10,04</t>
+          <t>-100,0; 5,56</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,36</t>
+          <t>13,31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 9,67</t>
+          <t>-34,92; 8,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 24,91</t>
+          <t>-5,6; 21,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 36,67</t>
+          <t>-14,16; 33,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 37,66</t>
+          <t>-7,59; 33,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 35,53</t>
+          <t>-71,37; 34,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-63,24; —</t>
+          <t>-53,45; 715,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-69,03; —</t>
+          <t>-77,32; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 153,23</t>
+          <t>-16,78; 133,06</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-9,32</t>
+          <t>-9,67</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-15,24%</t>
+          <t>-15,87%</t>
         </is>
       </c>
     </row>
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 26,81</t>
+          <t>-7,9; 27,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 3,36</t>
+          <t>-38,17; 0,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 11,44</t>
+          <t>-12,98; 13,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 25,01</t>
+          <t>-45,56; 29,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 132,88</t>
+          <t>-25,15; 140,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-92,3; 71,98</t>
+          <t>-100,0; 45,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 54,8</t>
+          <t>-62,91; 73,51</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 8,21</t>
+          <t>-11,39; 8,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,66</t>
+          <t>-3,18; 10,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,35</t>
+          <t>-8,63; 5,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 4,52</t>
+          <t>-9,03; 9,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 23,79</t>
+          <t>-26,31; 23,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 110,75</t>
+          <t>-18,56; 101,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 45,66</t>
+          <t>-50,61; 55,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 14,21</t>
+          <t>-23,51; 31,83</t>
         </is>
       </c>
     </row>
